--- a/TestData/Book1.xlsx
+++ b/TestData/Book1.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{AF209E5A-308D-4AF9-B28A-5798DC137E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\actno\OneDrive\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D1D36A-E223-4079-AC74-11C2C8D28334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3AAD22F3-5CD7-4742-896E-5D1D8719418E}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7450" xr2:uid="{3AAD22F3-5CD7-4742-896E-5D1D8719418E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>EmailId</t>
   </si>
@@ -60,9 +73,6 @@
   </si>
   <si>
     <t>234567wert</t>
-  </si>
-  <si>
-    <t>invalid</t>
   </si>
 </sst>
 </file>
@@ -462,18 +472,18 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>9</v>
       </c>
       <c r="B4" t="s">
@@ -491,14 +501,12 @@
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A5" r:id="rId1" xr:uid="{794DA81F-445F-47EB-AE93-E5AF1411B704}"/>
-    <hyperlink ref="A3" r:id="rId2" xr:uid="{E82D607B-DD83-474B-8706-048DDA3E8E20}"/>
-    <hyperlink ref="A4" r:id="rId3" xr:uid="{E9BFF900-B42C-4538-BF88-C0137DAA9311}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
